--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_AD4D361C20488DEA4E38A052645D5ADC5ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED3B1049-AB5C-48FA-8AE7-E4CC53BF76D0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31140" yWindow="2550" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>e-mail</t>
   </si>
   <si>
     <t>jonattasneves@hotmail.com</t>
+  </si>
+  <si>
+    <t>marketing@viastar.com.br</t>
+  </si>
+  <si>
+    <t>lucasvitorclaro@hotmail.com.br</t>
   </si>
 </sst>
 </file>
@@ -96,12 +102,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -383,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -399,9 +406,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{350DF397-C529-4AC0-83E4-8320038028AC}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{8CD1FED3-EDB2-4F49-A242-DDC9A4511EA0}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{A52FDE87-0ED6-4602-92D5-9BA835AB1ABA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9E60981-0F53-40AE-8EB1-7E237E925C79}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>marketing@viastar.com.br</t>
   </si>
   <si>
-    <t>lucasvitorclaro@hotmail.com.br</t>
+    <t>lucasvitorclaro@hotmail.com</t>
   </si>
 </sst>
 </file>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9E60981-0F53-40AE-8EB1-7E237E925C79}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0516B1-32D5-45E3-B0EA-681EBA2969D9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>e-mail</t>
   </si>
   <si>
     <t>jonattasneves@hotmail.com</t>
-  </si>
-  <si>
-    <t>marketing@viastar.com.br</t>
   </si>
   <si>
     <t>lucasvitorclaro@hotmail.com</t>
@@ -102,13 +99,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -125,6 +121,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
@@ -407,20 +407,14 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{350DF397-C529-4AC0-83E4-8320038028AC}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{8CD1FED3-EDB2-4F49-A242-DDC9A4511EA0}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{A52FDE87-0ED6-4602-92D5-9BA835AB1ABA}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{A52FDE87-0ED6-4602-92D5-9BA835AB1ABA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F29179-96B4-433D-A2A2-5C536B9209E7}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5818FF50-3893-4743-ACA2-2E6192598A25}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>jonattasneves@hotmail.com</t>
   </si>
   <si>
-    <t>jonatas.neves@viastar.com</t>
+    <t>jonatas.neves@viastar.com.br</t>
   </si>
   <si>
-    <t>lucas.vitor@viastar.com</t>
+    <t>lucas.vitor@viastar.com,br</t>
   </si>
 </sst>
 </file>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5818FF50-3893-4743-ACA2-2E6192598A25}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33222678-8F14-4E92-88BA-6F2BC617A14C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,18 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>e-mail</t>
   </si>
   <si>
-    <t>jonattasneves@hotmail.com</t>
-  </si>
-  <si>
-    <t>jonatas.neves@viastar.com.br</t>
-  </si>
-  <si>
-    <t>lucas.vitor@viastar.com,br</t>
+    <t>lucas.vitor@viastar.com.br</t>
   </si>
 </sst>
 </file>
@@ -405,25 +399,19 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{350DF397-C529-4AC0-83E4-8320038028AC}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{A52FDE87-0ED6-4602-92D5-9BA835AB1ABA}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{83828124-D2A9-4390-89E0-B90D3621A2E0}"/>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{83828124-D2A9-4390-89E0-B90D3621A2E0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,29 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33222678-8F14-4E92-88BA-6F2BC617A14C}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50942F3A-0BD4-42B4-8F02-92AAD541B2D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>e-mail</t>
   </si>
   <si>
     <t>lucas.vitor@viastar.com.br</t>
+  </si>
+  <si>
+    <t>jonattasneves@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -402,7 +416,9 @@
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -412,6 +428,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{83828124-D2A9-4390-89E0-B90D3621A2E0}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{C6786CCB-F3FE-4887-A9D6-BFB158ACC1CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/contatos.xlsx
+++ b/contatos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://viastarcombr-my.sharepoint.com/personal/lucas_vitor_viastar_com_br/Documents/Área de Trabalho/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8AE0E96-1021-45D3-ABDD-EE7A55847B9E}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{B05841DD-0383-4142-B3B1-D343E74A7797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF29A137-7F73-4E1D-B8EC-E4E7320894B6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1044" yWindow="1152" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
     <t>roni@viastar.com.br</t>
   </si>
   <si>
-    <t>E-MAIL</t>
+    <t>e-mail</t>
   </si>
 </sst>
 </file>
@@ -217,7 +217,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
